--- a/Result/profitability/3272.xlsx
+++ b/Result/profitability/3272.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM64"/>
+  <dimension ref="A1:AM65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-1.07</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.59625</v>
+        <v>-1.61875</v>
       </c>
       <c r="N2" t="n">
-        <v>9.675000000000001</v>
+        <v>9.04875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.16</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4825</v>
+        <v>-1.6175</v>
       </c>
       <c r="N3" t="n">
-        <v>10.03375</v>
+        <v>8.873749999999999</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-1.09</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5975</v>
+        <v>-1.675</v>
       </c>
       <c r="N4" t="n">
-        <v>10.275</v>
+        <v>8.96875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.33</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4775</v>
+        <v>-1.46125</v>
       </c>
       <c r="N5" t="n">
-        <v>11.015</v>
+        <v>10.66375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.14</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2875</v>
+        <v>-1.07375</v>
       </c>
       <c r="N6" t="n">
-        <v>12.6</v>
+        <v>12.24875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.16</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8975</v>
+        <v>-0.7175</v>
       </c>
       <c r="N7" t="n">
-        <v>14.4625</v>
+        <v>14.7125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -8556,6 +8556,133 @@
       </c>
       <c r="AM64" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>3272</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>726</v>
+      </c>
+      <c r="D65" t="n">
+        <v>693</v>
+      </c>
+      <c r="E65" t="n">
+        <v>33</v>
+      </c>
+      <c r="F65" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="G65" t="n">
+        <v>-51</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-7.04%</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>-17</v>
+      </c>
+      <c r="J65" t="n">
+        <v>-68</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-75</v>
+      </c>
+      <c r="L65" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="M65" t="n">
+        <v>-1.61875</v>
+      </c>
+      <c r="N65" t="n">
+        <v>8.376250000000001</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X65" t="n">
+        <v>-0.5535714285714286</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>-2.57</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>-0.3629943502824859</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>0.1299999999999999</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>-0.09420289855072461</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>-2.81</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>-0.3838797814207651</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK65" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
